--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -31,6 +31,9 @@
   </si>
   <si>
     <t>Rank</t>
+  </si>
+  <si>
+    <t>Attribute</t>
   </si>
   <si>
     <t>EquipmentId</t>
@@ -59,10 +62,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -81,7 +84,122 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -96,129 +214,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,187 +236,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,11 +430,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -446,16 +455,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -475,26 +484,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -510,17 +499,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -532,7 +535,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -541,136 +544,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1042,7 +1045,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="7.54545454545455" customWidth="1"/>
+    <col min="4" max="4" width="10.2727272727273" customWidth="1"/>
     <col min="5" max="5" width="9" style="2"/>
     <col min="6" max="6" width="6.18181818181818" customWidth="1"/>
     <col min="7" max="8" width="6.81818181818182" customWidth="1"/>
@@ -1068,21 +1071,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1"/>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" s="2"/>
-      <c r="I1"/>
       <c r="J1" s="2"/>
-      <c r="K1"/>
       <c r="L1" s="2"/>
-      <c r="M1"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
-      <c r="P1"/>
-      <c r="Q1"/>
-      <c r="R1"/>
-      <c r="S1"/>
-      <c r="T1"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
     </row>
@@ -1101,9 +1097,11 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="H2" s="2"/>
       <c r="J2" s="2"/>
       <c r="L2" s="2"/>
@@ -1127,9 +1125,11 @@
         <v>1010</v>
       </c>
       <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
@@ -1146,9 +1146,11 @@
         <v>1020</v>
       </c>
       <c r="E4">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="5:6">
       <c r="E5"/>
@@ -1218,13 +1220,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1490,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1498,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1506,9 +1508,8 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3"/>
+        <v>11</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
@@ -1517,9 +1518,8 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4"/>
+        <v>12</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -55,6 +55,42 @@
   </si>
   <si>
     <t>ハウレス</t>
+  </si>
+  <si>
+    <t>パティン</t>
+  </si>
+  <si>
+    <t>マルコシアス</t>
+  </si>
+  <si>
+    <t>マルファス</t>
+  </si>
+  <si>
+    <t>セーレ</t>
+  </si>
+  <si>
+    <t>フォカロル</t>
+  </si>
+  <si>
+    <t>ウヴァル</t>
+  </si>
+  <si>
+    <t>クロセル</t>
+  </si>
+  <si>
+    <t>プルソン</t>
+  </si>
+  <si>
+    <t>アンドロマリウス</t>
+  </si>
+  <si>
+    <t>ロイム</t>
+  </si>
+  <si>
+    <t>パイモン</t>
+  </si>
+  <si>
+    <t>フルカス</t>
   </si>
 </sst>
 </file>
@@ -62,10 +98,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -84,7 +120,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -93,6 +152,58 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -114,84 +225,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -206,15 +241,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,187 +272,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,6 +463,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -445,11 +490,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -469,32 +520,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -508,11 +538,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,145 +571,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1041,10 +1077,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="3" max="3" width="11.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
     <col min="4" max="4" width="10.2727272727273" customWidth="1"/>
     <col min="5" max="5" width="9" style="2"/>
     <col min="6" max="6" width="6.18181818181818" customWidth="1"/>
@@ -1152,53 +1188,278 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="5:6">
-      <c r="E5"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="5:6">
-      <c r="E6"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="5:6">
-      <c r="E7"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="5:6">
-      <c r="E8"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="5:6">
-      <c r="E9"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="5:6">
-      <c r="E10"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="5:6">
-      <c r="E11"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="5:6">
-      <c r="E12"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="5:6">
-      <c r="E13"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="5:6">
-      <c r="E14"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="5:6">
-      <c r="E15"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="5:6">
-      <c r="E16"/>
-      <c r="F16" s="2"/>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>1030</v>
+      </c>
+      <c r="B5">
+        <v>1030</v>
+      </c>
+      <c r="C5" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
+        <v>パティン</v>
+      </c>
+      <c r="D5">
+        <v>1030</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>2010</v>
+      </c>
+      <c r="B6">
+        <v>2010</v>
+      </c>
+      <c r="C6" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
+        <v>マルコシアス</v>
+      </c>
+      <c r="D6">
+        <v>2010</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2020</v>
+      </c>
+      <c r="B7">
+        <v>2020</v>
+      </c>
+      <c r="C7" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
+        <v>マルファス</v>
+      </c>
+      <c r="D7">
+        <v>2020</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>2030</v>
+      </c>
+      <c r="B8">
+        <v>2030</v>
+      </c>
+      <c r="C8" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
+        <v>セーレ</v>
+      </c>
+      <c r="D8">
+        <v>2030</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>3010</v>
+      </c>
+      <c r="B9">
+        <v>3010</v>
+      </c>
+      <c r="C9" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
+        <v>フォカロル</v>
+      </c>
+      <c r="D9">
+        <v>3010</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>3020</v>
+      </c>
+      <c r="B10">
+        <v>3020</v>
+      </c>
+      <c r="C10" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
+        <v>ウヴァル</v>
+      </c>
+      <c r="D10">
+        <v>3020</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>3030</v>
+      </c>
+      <c r="B11">
+        <v>3030</v>
+      </c>
+      <c r="C11" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
+        <v>クロセル</v>
+      </c>
+      <c r="D11">
+        <v>3030</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>4010</v>
+      </c>
+      <c r="B12">
+        <v>4010</v>
+      </c>
+      <c r="C12" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
+        <v>プルソン</v>
+      </c>
+      <c r="D12">
+        <v>4010</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>4020</v>
+      </c>
+      <c r="B13">
+        <v>4020</v>
+      </c>
+      <c r="C13" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
+        <v>アンドロマリウス</v>
+      </c>
+      <c r="D13">
+        <v>4020</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>4030</v>
+      </c>
+      <c r="B14">
+        <v>4030</v>
+      </c>
+      <c r="C14" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
+        <v>ウヴァル</v>
+      </c>
+      <c r="D14">
+        <v>4030</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>5010</v>
+      </c>
+      <c r="B15">
+        <v>5010</v>
+      </c>
+      <c r="C15" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
+        <v>ロイム</v>
+      </c>
+      <c r="D15">
+        <v>5010</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>5020</v>
+      </c>
+      <c r="B16">
+        <v>5020</v>
+      </c>
+      <c r="C16" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="D16">
+        <v>5020</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>5030</v>
+      </c>
+      <c r="B17">
+        <v>5030</v>
+      </c>
+      <c r="C17" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
+        <v>フルカス</v>
+      </c>
+      <c r="D17">
+        <v>5030</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1210,7 +1471,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1245,7 +1506,7 @@
         <v>1010</v>
       </c>
       <c r="B3">
-        <v>11020</v>
+        <v>501010</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1262,86 +1523,302 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5"/>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6"/>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9"/>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10"/>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11"/>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12"/>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="3"/>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20"/>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="3"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23"/>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24"/>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25"/>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26"/>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27"/>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30"/>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31"/>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1020</v>
+      </c>
+      <c r="B5">
+        <v>501020</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>1030</v>
+      </c>
+      <c r="B6">
+        <v>11080</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>1030</v>
+      </c>
+      <c r="B7">
+        <v>501030</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>2010</v>
+      </c>
+      <c r="B8">
+        <v>12020</v>
+      </c>
+      <c r="C8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:3">
+      <c r="A9">
+        <v>2010</v>
+      </c>
+      <c r="B9">
+        <v>502010</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>2020</v>
+      </c>
+      <c r="B10">
+        <v>12030</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>2020</v>
+      </c>
+      <c r="B11">
+        <v>502020</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>2030</v>
+      </c>
+      <c r="B12">
+        <v>12050</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>2030</v>
+      </c>
+      <c r="B13">
+        <v>502030</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>3010</v>
+      </c>
+      <c r="B14">
+        <v>13010</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>3010</v>
+      </c>
+      <c r="B15">
+        <v>503010</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>3020</v>
+      </c>
+      <c r="B16">
+        <v>13120</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>3020</v>
+      </c>
+      <c r="B17">
+        <v>503020</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>3030</v>
+      </c>
+      <c r="B18">
+        <v>13130</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>3030</v>
+      </c>
+      <c r="B19">
+        <v>503030</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>4010</v>
+      </c>
+      <c r="B20">
+        <v>14050</v>
+      </c>
+      <c r="C20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>4010</v>
+      </c>
+      <c r="B21">
+        <v>504010</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>4020</v>
+      </c>
+      <c r="B22">
+        <v>14120</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>4020</v>
+      </c>
+      <c r="B23">
+        <v>504020</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>4030</v>
+      </c>
+      <c r="B24">
+        <v>14030</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>4030</v>
+      </c>
+      <c r="B25">
+        <v>504030</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>5010</v>
+      </c>
+      <c r="B26">
+        <v>15120</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>5010</v>
+      </c>
+      <c r="B27">
+        <v>505010</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>5020</v>
+      </c>
+      <c r="B28">
+        <v>15010</v>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>5020</v>
+      </c>
+      <c r="B29">
+        <v>505020</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>5030</v>
+      </c>
+      <c r="B30">
+        <v>15130</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>5030</v>
+      </c>
+      <c r="B31">
+        <v>505030</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32"/>
@@ -1353,13 +1830,13 @@
       <c r="B34"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="3"/>
+      <c r="B35"/>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="3"/>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37"/>
+      <c r="B37" s="3"/>
     </row>
     <row r="38" spans="2:2">
       <c r="B38"/>
@@ -1449,13 +1926,13 @@
       <c r="B66"/>
     </row>
     <row r="67" spans="2:2">
-      <c r="B67" s="3"/>
+      <c r="B67"/>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="3"/>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69"/>
+      <c r="B69" s="3"/>
     </row>
     <row r="70" spans="2:2">
       <c r="B70"/>
@@ -1468,6 +1945,9 @@
     </row>
     <row r="73" spans="2:2">
       <c r="B73"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1478,7 +1958,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="11.8181818181818" customWidth="1"/>
@@ -1523,46 +2003,126 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="4:5">
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>1030</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="4:4">
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2010</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="4:5">
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>2020</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="4:5">
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>2030</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="4:5">
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>3010</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>3020</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="4:5">
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>3030</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="4:4">
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>4010</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="4:4">
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>4020</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="4:4">
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>4030</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="4:4">
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>5010</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="4:4">
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>5020</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
       <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>5030</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -27,7 +27,7 @@
     <t>_</t>
   </si>
   <si>
-    <t>ImagePath</t>
+    <t>IconIndex</t>
   </si>
   <si>
     <t>Rank</t>
@@ -45,6 +45,9 @@
     <t>LearningRate</t>
   </si>
   <si>
+    <t>EquipmentOnly</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
   </si>
   <si>
     <t>フルカス</t>
+  </si>
+  <si>
+    <t>ナベリウス</t>
   </si>
 </sst>
 </file>
@@ -98,10 +104,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -119,68 +125,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,16 +149,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,24 +193,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,7 +225,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,6 +237,37 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -272,25 +278,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -302,157 +428,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -463,15 +469,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -505,17 +502,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,15 +516,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,6 +535,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -571,145 +577,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1077,7 +1083,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1130,7 +1136,7 @@
         <v>装備なし</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1158,7 +1164,7 @@
         <v>アミィ</v>
       </c>
       <c r="D3">
-        <v>1010</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1179,7 +1185,7 @@
         <v>ハウレス</v>
       </c>
       <c r="D4">
-        <v>1020</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1200,7 +1206,7 @@
         <v>パティン</v>
       </c>
       <c r="D5">
-        <v>1030</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1221,7 +1227,7 @@
         <v>マルコシアス</v>
       </c>
       <c r="D6">
-        <v>2010</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1242,7 +1248,7 @@
         <v>マルファス</v>
       </c>
       <c r="D7">
-        <v>2020</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1263,7 +1269,7 @@
         <v>セーレ</v>
       </c>
       <c r="D8">
-        <v>2030</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1284,7 +1290,7 @@
         <v>フォカロル</v>
       </c>
       <c r="D9">
-        <v>3010</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1305,7 +1311,7 @@
         <v>ウヴァル</v>
       </c>
       <c r="D10">
-        <v>3020</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1326,7 +1332,7 @@
         <v>クロセル</v>
       </c>
       <c r="D11">
-        <v>3030</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1347,7 +1353,7 @@
         <v>プルソン</v>
       </c>
       <c r="D12">
-        <v>4010</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1368,7 +1374,7 @@
         <v>アンドロマリウス</v>
       </c>
       <c r="D13">
-        <v>4020</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1389,7 +1395,7 @@
         <v>ウヴァル</v>
       </c>
       <c r="D14">
-        <v>4030</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1410,7 +1416,7 @@
         <v>ロイム</v>
       </c>
       <c r="D15">
-        <v>5010</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1431,7 +1437,7 @@
         <v>パイモン</v>
       </c>
       <c r="D16">
-        <v>5020</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1452,13 +1458,34 @@
         <v>フルカス</v>
       </c>
       <c r="D17">
-        <v>5030</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
         <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>6010</v>
+      </c>
+      <c r="B18">
+        <v>6010</v>
+      </c>
+      <c r="C18" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
+        <v>ナベリウス</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1471,15 +1498,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C74"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:D74"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10.9090909090909" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.9090909090909" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1489,8 +1516,11 @@
       <c r="C1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1010</v>
       </c>
@@ -1500,8 +1530,11 @@
       <c r="C2">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1010</v>
       </c>
@@ -1511,8 +1544,11 @@
       <c r="C3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1020</v>
       </c>
@@ -1522,8 +1558,11 @@
       <c r="C4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1020</v>
       </c>
@@ -1533,8 +1572,11 @@
       <c r="C5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1030</v>
       </c>
@@ -1544,8 +1586,11 @@
       <c r="C6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1030</v>
       </c>
@@ -1555,8 +1600,11 @@
       <c r="C7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>2010</v>
       </c>
@@ -1566,8 +1614,11 @@
       <c r="C8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:3">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:4">
       <c r="A9">
         <v>2010</v>
       </c>
@@ -1577,8 +1628,11 @@
       <c r="C9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>2020</v>
       </c>
@@ -1588,8 +1642,11 @@
       <c r="C10">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>2020</v>
       </c>
@@ -1599,8 +1656,11 @@
       <c r="C11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>2030</v>
       </c>
@@ -1610,8 +1670,11 @@
       <c r="C12">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>2030</v>
       </c>
@@ -1621,8 +1684,11 @@
       <c r="C13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>3010</v>
       </c>
@@ -1632,8 +1698,11 @@
       <c r="C14">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>3010</v>
       </c>
@@ -1643,8 +1712,11 @@
       <c r="C15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>3020</v>
       </c>
@@ -1654,8 +1726,11 @@
       <c r="C16">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>3020</v>
       </c>
@@ -1665,8 +1740,11 @@
       <c r="C17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>3030</v>
       </c>
@@ -1676,8 +1754,11 @@
       <c r="C18">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>3030</v>
       </c>
@@ -1687,8 +1768,11 @@
       <c r="C19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>4010</v>
       </c>
@@ -1698,8 +1782,11 @@
       <c r="C20">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>4010</v>
       </c>
@@ -1709,8 +1796,11 @@
       <c r="C21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>4020</v>
       </c>
@@ -1720,8 +1810,11 @@
       <c r="C22">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>4020</v>
       </c>
@@ -1731,8 +1824,11 @@
       <c r="C23">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>4030</v>
       </c>
@@ -1742,8 +1838,11 @@
       <c r="C24">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>4030</v>
       </c>
@@ -1753,8 +1852,11 @@
       <c r="C25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>5010</v>
       </c>
@@ -1764,8 +1866,11 @@
       <c r="C26">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>5010</v>
       </c>
@@ -1775,8 +1880,11 @@
       <c r="C27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>5020</v>
       </c>
@@ -1786,8 +1894,11 @@
       <c r="C28">
         <v>20</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>5020</v>
       </c>
@@ -1797,8 +1908,11 @@
       <c r="C29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>5030</v>
       </c>
@@ -1808,8 +1922,11 @@
       <c r="C30">
         <v>20</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>5030</v>
       </c>
@@ -1819,9 +1936,23 @@
       <c r="C31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32"/>
+      <c r="D31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>6010</v>
+      </c>
+      <c r="B32">
+        <v>506010</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33"/>
@@ -1958,7 +2089,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="11.8181818181818" customWidth="1"/>
@@ -1972,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1980,7 +2111,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1988,7 +2119,7 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1998,7 +2129,7 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2008,7 +2139,7 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -2018,7 +2149,7 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -2027,7 +2158,7 @@
         <v>2020</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2037,7 +2168,7 @@
         <v>2030</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2047,7 +2178,7 @@
         <v>3010</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2057,7 +2188,7 @@
         <v>3020</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -2066,7 +2197,7 @@
         <v>3030</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2076,7 +2207,7 @@
         <v>4010</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -2085,7 +2216,7 @@
         <v>4020</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -2094,7 +2225,7 @@
         <v>4030</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1"/>
     </row>
@@ -2103,7 +2234,7 @@
         <v>5010</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2112,7 +2243,7 @@
         <v>5020</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -2121,7 +2252,15 @@
         <v>5030</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>6010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Attribute</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>EquipmentId</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
   </si>
   <si>
     <t>ナベリウス</t>
+  </si>
+  <si>
+    <t>アンドレアルフス</t>
   </si>
 </sst>
 </file>
@@ -125,30 +131,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -158,14 +140,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -179,7 +154,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,15 +168,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -216,39 +215,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,11 +239,41 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -278,55 +284,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,91 +416,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,12 +458,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -447,18 +465,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -469,6 +475,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -502,20 +519,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,17 +549,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -561,11 +569,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,7 +583,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -586,136 +592,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1083,7 +1089,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1485,6 +1491,27 @@
         <v>11</v>
       </c>
       <c r="F18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>6020</v>
+      </c>
+      <c r="B19">
+        <v>6020</v>
+      </c>
+      <c r="C19" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
+        <v>アンドレアルフス</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19">
         <v>6</v>
       </c>
     </row>
@@ -1508,16 +1535,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1954,8 +1981,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:2">
-      <c r="B33"/>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>6020</v>
+      </c>
+      <c r="B33">
+        <v>506020</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34"/>
@@ -2089,7 +2127,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="11.8181818181818" customWidth="1"/>
@@ -2103,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2111,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2119,7 +2157,7 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2129,7 +2167,7 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2139,7 +2177,7 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -2149,7 +2187,7 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -2158,7 +2196,7 @@
         <v>2020</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2168,7 +2206,7 @@
         <v>2030</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2178,7 +2216,7 @@
         <v>3010</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2188,7 +2226,7 @@
         <v>3020</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1"/>
     </row>
@@ -2197,7 +2235,7 @@
         <v>3030</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2207,7 +2245,7 @@
         <v>4010</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -2216,7 +2254,7 @@
         <v>4020</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -2225,7 +2263,7 @@
         <v>4030</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1"/>
     </row>
@@ -2234,7 +2272,7 @@
         <v>5010</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2243,7 +2281,7 @@
         <v>5020</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -2252,7 +2290,7 @@
         <v>5030</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2260,7 +2298,15 @@
         <v>6010</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>6020</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Attribute</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>EquipmentId</t>
   </si>
   <si>
@@ -66,6 +63,9 @@
     <t>パティン</t>
   </si>
   <si>
+    <t>シトリ</t>
+  </si>
+  <si>
     <t>マルコシアス</t>
   </si>
   <si>
@@ -75,6 +75,9 @@
     <t>セーレ</t>
   </si>
   <si>
+    <t>ハルパス</t>
+  </si>
+  <si>
     <t>フォカロル</t>
   </si>
   <si>
@@ -84,12 +87,18 @@
     <t>クロセル</t>
   </si>
   <si>
+    <t>ハアゲンティ</t>
+  </si>
+  <si>
     <t>プルソン</t>
   </si>
   <si>
     <t>アンドロマリウス</t>
   </si>
   <si>
+    <t>ヴァラク</t>
+  </si>
+  <si>
     <t>ロイム</t>
   </si>
   <si>
@@ -97,6 +106,9 @@
   </si>
   <si>
     <t>フルカス</t>
+  </si>
+  <si>
+    <t>マルバス</t>
   </si>
   <si>
     <t>ナベリウス</t>
@@ -111,9 +123,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -138,14 +150,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -154,7 +158,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,17 +172,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,8 +201,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -201,6 +211,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -222,11 +239,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -235,27 +260,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -268,10 +272,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -284,13 +296,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -302,25 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -332,139 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,17 +487,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -500,6 +501,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -519,6 +529,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -530,6 +549,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -551,27 +579,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -583,145 +595,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1089,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1221,37 +1233,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" customFormat="1" spans="1:6">
       <c r="A6">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B6">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="C6" t="str">
         <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
-        <v>マルコシアス</v>
+        <v>シトリ</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B7">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C7" t="str">
         <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
-        <v>マルファス</v>
+        <v>マルコシアス</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1265,14 +1277,14 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B8">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C8" t="str">
         <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
-        <v>セーレ</v>
+        <v>マルファス</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1286,56 +1298,56 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B9">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="C9" t="str">
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>フォカロル</v>
+        <v>セーレ</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
       <c r="A10">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="B10">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>ウヴァル</v>
+        <v>ハルパス</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B11">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="C11" t="str">
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>クロセル</v>
+        <v>フォカロル</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -1349,169 +1361,274 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B12">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>プルソン</v>
+        <v>ウヴァル</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>4020</v>
+        <v>3030</v>
       </c>
       <c r="B13">
-        <v>4020</v>
+        <v>3030</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
-        <v>アンドロマリウス</v>
+        <v>クロセル</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
       <c r="A14">
-        <v>4030</v>
+        <v>3040</v>
       </c>
       <c r="B14">
-        <v>4030</v>
+        <v>3040</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
-        <v>ウヴァル</v>
+        <v>ハアゲンティ</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B15">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>ロイム</v>
+        <v>プルソン</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B16">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>アンドロマリウス</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>5030</v>
+        <v>4030</v>
       </c>
       <c r="B17">
-        <v>5030</v>
+        <v>4030</v>
       </c>
       <c r="C17" t="str">
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
-        <v>フルカス</v>
+        <v>ウヴァル</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>6010</v>
+        <v>4040</v>
       </c>
       <c r="B18">
-        <v>6010</v>
+        <v>4040</v>
       </c>
       <c r="C18" t="str">
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
-        <v>ナベリウス</v>
+        <v>ヴァラク</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>6020</v>
+        <v>5010</v>
       </c>
       <c r="B19">
-        <v>6020</v>
+        <v>5010</v>
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
+        <v>ロイム</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>5020</v>
+      </c>
+      <c r="B20">
+        <v>5020</v>
+      </c>
+      <c r="C20" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>5030</v>
+      </c>
+      <c r="B21">
+        <v>5030</v>
+      </c>
+      <c r="C21" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
+        <v>フルカス</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
+      <c r="A22">
+        <v>5040</v>
+      </c>
+      <c r="B22">
+        <v>5040</v>
+      </c>
+      <c r="C22" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
+        <v>マルバス</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>6010</v>
+      </c>
+      <c r="B23">
+        <v>6010</v>
+      </c>
+      <c r="C23" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
+        <v>ナベリウス</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>11</v>
+      </c>
+      <c r="F23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>6020</v>
+      </c>
+      <c r="B24">
+        <v>6020</v>
+      </c>
+      <c r="C24" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
         <v>アンドレアルフス</v>
       </c>
-      <c r="D19">
+      <c r="D24">
         <v>6</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19">
+      <c r="E24">
+        <v>11</v>
+      </c>
+      <c r="F24">
         <v>6</v>
       </c>
     </row>
@@ -1525,7 +1642,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1535,16 +1652,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1569,7 +1686,7 @@
         <v>501010</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1597,7 +1714,7 @@
         <v>501020</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1625,7 +1742,7 @@
         <v>501030</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1633,38 +1750,38 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B8">
-        <v>12020</v>
+        <v>501040</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B9">
-        <v>502010</v>
+        <v>501041</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B10">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -1673,15 +1790,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" customFormat="1" spans="1:4">
       <c r="A11">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B11">
-        <v>502020</v>
+        <v>502010</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1689,10 +1806,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B12">
-        <v>12050</v>
+        <v>12030</v>
       </c>
       <c r="C12">
         <v>20</v>
@@ -1703,13 +1820,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B13">
-        <v>502030</v>
+        <v>502020</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1717,10 +1834,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B14">
-        <v>13010</v>
+        <v>12050</v>
       </c>
       <c r="C14">
         <v>20</v>
@@ -1731,13 +1848,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B15">
-        <v>503010</v>
+        <v>502030</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1745,38 +1862,38 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="B16">
-        <v>13120</v>
+        <v>502040</v>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="B17">
-        <v>503020</v>
+        <v>502041</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B18">
-        <v>13130</v>
+        <v>13010</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -1787,13 +1904,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B19">
-        <v>503030</v>
+        <v>503010</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1801,10 +1918,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B20">
-        <v>14050</v>
+        <v>13120</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -1815,13 +1932,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B21">
-        <v>504010</v>
+        <v>503020</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1829,10 +1946,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>4020</v>
+        <v>3030</v>
       </c>
       <c r="B22">
-        <v>14120</v>
+        <v>13130</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -1843,13 +1960,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>4020</v>
+        <v>3030</v>
       </c>
       <c r="B23">
-        <v>504020</v>
+        <v>503030</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1857,38 +1974,38 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>4030</v>
+        <v>3040</v>
       </c>
       <c r="B24">
-        <v>14030</v>
+        <v>503040</v>
       </c>
       <c r="C24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>4030</v>
+        <v>3040</v>
       </c>
       <c r="B25">
-        <v>504030</v>
+        <v>503041</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B26">
-        <v>15120</v>
+        <v>14050</v>
       </c>
       <c r="C26">
         <v>20</v>
@@ -1899,13 +2016,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B27">
-        <v>505010</v>
+        <v>504010</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1913,10 +2030,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B28">
-        <v>15010</v>
+        <v>14120</v>
       </c>
       <c r="C28">
         <v>20</v>
@@ -1927,13 +2044,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B29">
-        <v>505020</v>
+        <v>504020</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1941,10 +2058,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>5030</v>
+        <v>4030</v>
       </c>
       <c r="B30">
-        <v>15130</v>
+        <v>14030</v>
       </c>
       <c r="C30">
         <v>20</v>
@@ -1955,13 +2072,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>5030</v>
+        <v>4030</v>
       </c>
       <c r="B31">
-        <v>505030</v>
+        <v>504030</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1969,10 +2086,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>6010</v>
+        <v>4040</v>
       </c>
       <c r="B32">
-        <v>506010</v>
+        <v>504040</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1983,50 +2100,138 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
+        <v>5010</v>
+      </c>
+      <c r="B33">
+        <v>15120</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>5010</v>
+      </c>
+      <c r="B34">
+        <v>505010</v>
+      </c>
+      <c r="C34">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>5020</v>
+      </c>
+      <c r="B35">
+        <v>15010</v>
+      </c>
+      <c r="C35">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>5020</v>
+      </c>
+      <c r="B36">
+        <v>505020</v>
+      </c>
+      <c r="C36">
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>5030</v>
+      </c>
+      <c r="B37">
+        <v>15130</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>5030</v>
+      </c>
+      <c r="B38">
+        <v>505030</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>5040</v>
+      </c>
+      <c r="B39">
+        <v>505040</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>6010</v>
+      </c>
+      <c r="B40">
+        <v>506010</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
         <v>6020</v>
       </c>
-      <c r="B33">
+      <c r="B41">
         <v>506020</v>
       </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38"/>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39"/>
-    </row>
-    <row r="40" spans="2:2">
-      <c r="B40"/>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41"/>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42"/>
     </row>
     <row r="43" spans="2:2">
-      <c r="B43"/>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" spans="2:2">
-      <c r="B44"/>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" spans="2:2">
       <c r="B45"/>
@@ -2098,10 +2303,10 @@
       <c r="B67"/>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="3"/>
+      <c r="B68"/>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="3"/>
+      <c r="B69"/>
     </row>
     <row r="70" spans="2:2">
       <c r="B70"/>
@@ -2117,6 +2322,27 @@
     </row>
     <row r="74" spans="2:2">
       <c r="B74"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2127,7 +2353,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="11.8181818181818" customWidth="1"/>
@@ -2141,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2149,7 +2375,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2157,7 +2383,7 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2167,7 +2393,7 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2177,99 +2403,102 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6">
+        <v>1040</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
         <v>2010</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>3030</v>
+      </c>
+      <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>4020</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>3040</v>
+      </c>
+      <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>4030</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
       <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B15" t="s">
         <v>24</v>
@@ -2278,35 +2507,79 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>5020</v>
+        <v>4020</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:4">
       <c r="A17">
+        <v>4030</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>4040</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>5010</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>5020</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
         <v>5030</v>
       </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:2">
+      <c r="A22">
+        <v>5040</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
         <v>6010</v>
       </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
         <v>6020</v>
       </c>
-      <c r="B19" t="s">
-        <v>28</v>
+      <c r="B24" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -81,19 +81,22 @@
     <t>フォカロル</t>
   </si>
   <si>
+    <t>デカラピア</t>
+  </si>
+  <si>
+    <t>クロセル</t>
+  </si>
+  <si>
+    <t>ハアゲンティ</t>
+  </si>
+  <si>
+    <t>プルソン</t>
+  </si>
+  <si>
+    <t>アンドロマリウス</t>
+  </si>
+  <si>
     <t>ウヴァル</t>
-  </si>
-  <si>
-    <t>クロセル</t>
-  </si>
-  <si>
-    <t>ハアゲンティ</t>
-  </si>
-  <si>
-    <t>プルソン</t>
-  </si>
-  <si>
-    <t>アンドロマリウス</t>
   </si>
   <si>
     <t>ヴァラク</t>
@@ -122,10 +125,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -144,6 +147,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -151,73 +177,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,41 +191,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,7 +209,82 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,187 +299,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -487,6 +490,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -501,63 +524,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -579,11 +545,48 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,145 +598,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1368,7 +1371,7 @@
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>ウヴァル</v>
+        <v>デカラピア</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -2519,7 +2522,7 @@
         <v>4030</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -2528,7 +2531,7 @@
         <v>4040</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1"/>
     </row>
@@ -2537,7 +2540,7 @@
         <v>5010</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -2546,7 +2549,7 @@
         <v>5020</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1"/>
     </row>
@@ -2555,7 +2558,7 @@
         <v>5030</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:2">
@@ -2563,7 +2566,7 @@
         <v>5040</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2571,7 +2574,7 @@
         <v>6010</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2579,7 +2582,7 @@
         <v>6020</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -54,70 +54,70 @@
     <t>装備なし</t>
   </si>
   <si>
-    <t>アミィ</t>
-  </si>
-  <si>
-    <t>ハウレス</t>
-  </si>
-  <si>
-    <t>パティン</t>
-  </si>
-  <si>
-    <t>シトリ</t>
-  </si>
-  <si>
-    <t>マルコシアス</t>
-  </si>
-  <si>
-    <t>マルファス</t>
-  </si>
-  <si>
-    <t>セーレ</t>
-  </si>
-  <si>
-    <t>ハルパス</t>
-  </si>
-  <si>
-    <t>フォカロル</t>
-  </si>
-  <si>
-    <t>デカラピア</t>
-  </si>
-  <si>
-    <t>クロセル</t>
-  </si>
-  <si>
-    <t>ハアゲンティ</t>
-  </si>
-  <si>
-    <t>プルソン</t>
-  </si>
-  <si>
-    <t>アンドロマリウス</t>
-  </si>
-  <si>
-    <t>ウヴァル</t>
-  </si>
-  <si>
-    <t>ヴァラク</t>
-  </si>
-  <si>
-    <t>ロイム</t>
-  </si>
-  <si>
-    <t>パイモン</t>
-  </si>
-  <si>
-    <t>フルカス</t>
-  </si>
-  <si>
-    <t>マルバス</t>
-  </si>
-  <si>
-    <t>ナベリウス</t>
-  </si>
-  <si>
-    <t>アンドレアルフス</t>
+    <t>炎砦の魔石</t>
+  </si>
+  <si>
+    <t>ブラストバングル</t>
+  </si>
+  <si>
+    <t>エルドチョーカー</t>
+  </si>
+  <si>
+    <t>火の化身のベルト</t>
+  </si>
+  <si>
+    <t>雷の結晶</t>
+  </si>
+  <si>
+    <t>トルドの雷針</t>
+  </si>
+  <si>
+    <t>雷神の指輪</t>
+  </si>
+  <si>
+    <t>電撃のタリスマン</t>
+  </si>
+  <si>
+    <t>ブリザードアンク</t>
+  </si>
+  <si>
+    <t>氷風の耳飾り</t>
+  </si>
+  <si>
+    <t>スヴェルの結界</t>
+  </si>
+  <si>
+    <t>巨人の首輪</t>
+  </si>
+  <si>
+    <t>アルフの光羽</t>
+  </si>
+  <si>
+    <t>聖光のリボン</t>
+  </si>
+  <si>
+    <t>グリンの金剛毛</t>
+  </si>
+  <si>
+    <t>アースブローチ</t>
+  </si>
+  <si>
+    <t>邪神のリング</t>
+  </si>
+  <si>
+    <t>ヨルムの魔鱗</t>
+  </si>
+  <si>
+    <t>ナグルファル片</t>
+  </si>
+  <si>
+    <t>呪われたコイン</t>
+  </si>
+  <si>
+    <t>ルーンのエングレ</t>
+  </si>
+  <si>
+    <t>ドヴェルグの指輪</t>
   </si>
 </sst>
 </file>
@@ -125,8 +125,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -146,26 +146,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -177,7 +176,53 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -201,7 +246,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -209,67 +261,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,7 +276,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,187 +299,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -490,17 +490,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -528,17 +517,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -554,24 +552,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,6 +575,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -598,145 +598,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C3" t="str">
         <f>INDEX(TextData!B:B,MATCH(B3,TextData!A:A))</f>
-        <v>アミィ</v>
+        <v>炎砦の魔石</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C4" t="str">
         <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
-        <v>ハウレス</v>
+        <v>ブラストバングル</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C5" t="str">
         <f>INDEX(TextData!B:B,MATCH(B5,TextData!A:A))</f>
-        <v>パティン</v>
+        <v>エルドチョーカー</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="str">
         <f>INDEX(TextData!B:B,MATCH(B6,TextData!A:A))</f>
-        <v>シトリ</v>
+        <v>火の化身のベルト</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C7" t="str">
         <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
-        <v>マルコシアス</v>
+        <v>雷の結晶</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C8" t="str">
         <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
-        <v>マルファス</v>
+        <v>トルドの雷針</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C9" t="str">
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>セーレ</v>
+        <v>雷神の指輪</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C10" t="str">
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>ハルパス</v>
+        <v>電撃のタリスマン</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C11" t="str">
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>フォカロル</v>
+        <v>ブリザードアンク</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>デカラピア</v>
+        <v>氷風の耳飾り</v>
       </c>
       <c r="D12">
         <v>3</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C13" t="str">
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
-        <v>クロセル</v>
+        <v>スヴェルの結界</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C14" t="str">
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
-        <v>ハアゲンティ</v>
+        <v>巨人の首輪</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>プルソン</v>
+        <v>アルフの光羽</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C16" t="str">
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>アンドロマリウス</v>
+        <v>聖光のリボン</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C17" t="str">
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
-        <v>ウヴァル</v>
+        <v>グリンの金剛毛</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C18" t="str">
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
-        <v>ヴァラク</v>
+        <v>アースブローチ</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
-        <v>ロイム</v>
+        <v>邪神のリング</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C20" t="str">
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ヨルムの魔鱗</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C21" t="str">
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
-        <v>フルカス</v>
+        <v>ナグルファル片</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>マルバス</v>
+        <v>呪われたコイン</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>ナベリウス</v>
+        <v>ルーンのエングレ</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>アンドレアルフス</v>
+        <v>ドヴェルグの指輪</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2359,7 +2359,7 @@
   <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="11.8181818181818" customWidth="1"/>
+    <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
     <col min="4" max="4" width="45.1818181818182" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -111,7 +111,7 @@
     <t>ナグルファル片</t>
   </si>
   <si>
-    <t>呪われたコイン</t>
+    <t>ウートの幻影鏡</t>
   </si>
   <si>
     <t>ルーンのエングレ</t>
@@ -125,10 +125,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -146,16 +146,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -163,28 +170,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,46 +184,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,16 +206,38 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,7 +252,39 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,6 +299,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -311,49 +323,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,121 +479,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -493,11 +493,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,17 +523,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,20 +552,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -575,21 +590,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -598,145 +598,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>呪われたコイン</v>
+        <v>ウートの幻影鏡</v>
       </c>
       <c r="D22">
         <v>5</v>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Id</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>ウートの幻影鏡</t>
+  </si>
+  <si>
+    <t>新兵のバングル</t>
   </si>
   <si>
     <t>ルーンのエングレ</t>
@@ -126,9 +129,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -146,6 +149,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -154,7 +180,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,37 +195,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,8 +217,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -230,16 +233,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -258,9 +270,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,17 +286,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,19 +302,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,163 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,16 +497,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -532,11 +535,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,11 +561,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -576,17 +583,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,145 +601,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1104,7 +1107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1593,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23">
         <v>6010</v>
       </c>
@@ -1602,13 +1605,13 @@
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>ルーンのエングレ</v>
+        <v>新兵のバングル</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>6</v>
@@ -1616,14 +1619,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>6020</v>
+        <v>7010</v>
       </c>
       <c r="B24">
-        <v>6020</v>
+        <v>7010</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>ドヴェルグの指輪</v>
+        <v>ルーンのエングレ</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -1632,6 +1635,27 @@
         <v>11</v>
       </c>
       <c r="F24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>7020</v>
+      </c>
+      <c r="B25">
+        <v>7020</v>
+      </c>
+      <c r="C25" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
+        <v>ドヴェルグの指輪</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>11</v>
+      </c>
+      <c r="F25">
         <v>6</v>
       </c>
     </row>
@@ -1645,7 +1669,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2215,10 +2239,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="B41">
-        <v>506020</v>
+        <v>506011</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2227,20 +2251,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
-      <c r="B42"/>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="3"/>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>7010</v>
+      </c>
+      <c r="B42">
+        <v>507010</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>7020</v>
+      </c>
+      <c r="B43">
+        <v>507020</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="2:2">
-      <c r="B44" s="3"/>
+      <c r="B44"/>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45"/>
+      <c r="B45" s="3"/>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46"/>
+      <c r="B46" s="3"/>
     </row>
     <row r="47" spans="2:2">
       <c r="B47"/>
@@ -2327,16 +2373,16 @@
       <c r="B74"/>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="3"/>
+      <c r="B75"/>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" s="3"/>
+      <c r="B76"/>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77"/>
+      <c r="B77" s="3"/>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78"/>
+      <c r="B78" s="3"/>
     </row>
     <row r="79" spans="2:2">
       <c r="B79"/>
@@ -2346,6 +2392,12 @@
     </row>
     <row r="81" spans="2:2">
       <c r="B81"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2356,7 +2408,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
@@ -2569,7 +2621,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" customFormat="1" spans="1:2">
       <c r="A23">
         <v>6010</v>
       </c>
@@ -2579,10 +2631,18 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>6020</v>
+        <v>7010</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>7020</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -128,10 +128,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -149,29 +149,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -186,6 +163,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -194,24 +201,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,15 +225,47 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,30 +286,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -302,37 +302,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,145 +440,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -493,21 +493,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -528,8 +513,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -546,24 +533,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -585,10 +554,41 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -601,7 +601,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -610,136 +610,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1669,7 +1669,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>7010</v>
+        <v>6010</v>
       </c>
       <c r="B42">
-        <v>507010</v>
+        <v>506012</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2267,32 +2267,54 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
+        <v>6010</v>
+      </c>
+      <c r="B43">
+        <v>506013</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>7010</v>
+      </c>
+      <c r="B44">
+        <v>507010</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
         <v>7020</v>
       </c>
-      <c r="B43">
+      <c r="B45">
         <v>507020</v>
       </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44"/>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="3"/>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" s="3"/>
+      <c r="B46"/>
     </row>
     <row r="47" spans="2:2">
-      <c r="B47"/>
+      <c r="B47" s="3"/>
     </row>
     <row r="48" spans="2:2">
-      <c r="B48"/>
+      <c r="B48" s="3"/>
     </row>
     <row r="49" spans="2:2">
       <c r="B49"/>
@@ -2379,16 +2401,16 @@
       <c r="B76"/>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77" s="3"/>
+      <c r="B77"/>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="3"/>
+      <c r="B78"/>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79"/>
+      <c r="B79" s="3"/>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80"/>
+      <c r="B80" s="3"/>
     </row>
     <row r="81" spans="2:2">
       <c r="B81"/>
@@ -2398,6 +2420,12 @@
     </row>
     <row r="83" spans="2:2">
       <c r="B83"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
   <si>
     <t>Id</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Text</t>
+  </si>
+  <si>
+    <t>EnglishText</t>
   </si>
   <si>
     <t>装備なし</t>
@@ -128,9 +131,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -150,7 +153,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -163,33 +188,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -203,7 +214,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,22 +250,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -249,33 +267,25 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -285,13 +295,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -302,19 +305,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,163 +485,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,10 +516,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -533,21 +534,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -570,6 +556,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -584,15 +596,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -601,145 +604,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2436,241 +2439,316 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="45.1818181818182" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="4" max="4" width="17.8454545454545" customWidth="1"/>
+    <col min="5" max="5" width="11.0727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>2010</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>2020</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>2030</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>2040</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>3030</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>3040</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>4010</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>4020</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>4030</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>4040</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>5010</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>5020</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>5030</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:2">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
       <c r="A22">
         <v>5040</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:2">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23">
         <v>6010</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>7010</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>34</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>7020</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -57,73 +57,145 @@
     <t>装備なし</t>
   </si>
   <si>
+    <t>No Equipment</t>
+  </si>
+  <si>
     <t>炎砦の魔石</t>
   </si>
   <si>
+    <t>Fortress Firestone</t>
+  </si>
+  <si>
     <t>ブラストバングル</t>
   </si>
   <si>
+    <t>Blast Bangle</t>
+  </si>
+  <si>
     <t>エルドチョーカー</t>
   </si>
   <si>
+    <t>Eld Choker</t>
+  </si>
+  <si>
     <t>火の化身のベルト</t>
   </si>
   <si>
+    <t>Avatar of Flame Belt</t>
+  </si>
+  <si>
     <t>雷の結晶</t>
   </si>
   <si>
+    <t>Thunder Crystal</t>
+  </si>
+  <si>
     <t>トルドの雷針</t>
   </si>
   <si>
+    <t>Trold Thunder Pin</t>
+  </si>
+  <si>
     <t>雷神の指輪</t>
   </si>
   <si>
+    <t>Thunder God Ring</t>
+  </si>
+  <si>
     <t>電撃のタリスマン</t>
   </si>
   <si>
+    <t>Lightning Talisman</t>
+  </si>
+  <si>
     <t>ブリザードアンク</t>
   </si>
   <si>
+    <t>Blizzard Ankh</t>
+  </si>
+  <si>
     <t>氷風の耳飾り</t>
   </si>
   <si>
+    <t>Icy Breeze Earring</t>
+  </si>
+  <si>
     <t>スヴェルの結界</t>
   </si>
   <si>
+    <t>Svel's Barrier</t>
+  </si>
+  <si>
     <t>巨人の首輪</t>
   </si>
   <si>
+    <t>Giant's Collar</t>
+  </si>
+  <si>
     <t>アルフの光羽</t>
   </si>
   <si>
+    <t>Alf's Light Feather</t>
+  </si>
+  <si>
     <t>聖光のリボン</t>
   </si>
   <si>
+    <t>Holy Ribbon</t>
+  </si>
+  <si>
     <t>グリンの金剛毛</t>
   </si>
   <si>
+    <t>Grin's Vajra Hair</t>
+  </si>
+  <si>
     <t>アースブローチ</t>
   </si>
   <si>
+    <t>Earth Brooch</t>
+  </si>
+  <si>
     <t>邪神のリング</t>
   </si>
   <si>
+    <t>Evil God Ring</t>
+  </si>
+  <si>
     <t>ヨルムの魔鱗</t>
   </si>
   <si>
+    <t>Yorm's Magic Scale</t>
+  </si>
+  <si>
     <t>ナグルファル片</t>
   </si>
   <si>
+    <t>Naglfar Fragment</t>
+  </si>
+  <si>
     <t>ウートの幻影鏡</t>
   </si>
   <si>
+    <t>Uot's Illusion Mirror</t>
+  </si>
+  <si>
     <t>新兵のバングル</t>
   </si>
   <si>
+    <t>New Recruit Bangle</t>
+  </si>
+  <si>
     <t>ルーンのエングレ</t>
   </si>
   <si>
+    <t>Rune Engraving</t>
+  </si>
+  <si>
     <t>ドヴェルグの指輪</t>
+  </si>
+  <si>
+    <t>Dvergr Ring</t>
   </si>
 </sst>
 </file>
@@ -131,10 +203,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -149,13 +221,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -175,7 +240,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,6 +256,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -204,9 +285,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,15 +324,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,17 +346,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,29 +367,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -305,25 +377,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -335,109 +545,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,43 +557,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -523,6 +595,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -534,35 +615,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -582,6 +634,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -596,6 +657,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -604,145 +676,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2446,6 +2518,7 @@
     <col min="3" max="3" width="20.5454545454545" customWidth="1"/>
     <col min="4" max="4" width="17.8454545454545" customWidth="1"/>
     <col min="5" max="5" width="11.0727272727273" customWidth="1"/>
+    <col min="6" max="6" width="20.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2467,7 +2540,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2475,12 +2548,12 @@
         <v>1010</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2488,12 +2561,12 @@
         <v>1020</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2501,12 +2574,12 @@
         <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2514,12 +2587,12 @@
         <v>1040</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2527,11 +2600,11 @@
         <v>2010</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1"/>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2539,12 +2612,12 @@
         <v>2020</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2552,12 +2625,12 @@
         <v>2030</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2565,12 +2638,12 @@
         <v>2040</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2578,12 +2651,12 @@
         <v>3010</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2591,11 +2664,11 @@
         <v>3020</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1"/>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2603,12 +2676,12 @@
         <v>3030</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2616,12 +2689,12 @@
         <v>3040</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2629,11 +2702,11 @@
         <v>4010</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1"/>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2641,11 +2714,11 @@
         <v>4020</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D16" s="1"/>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2653,11 +2726,11 @@
         <v>4030</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1"/>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2665,11 +2738,11 @@
         <v>4040</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D18" s="1"/>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2677,11 +2750,11 @@
         <v>5010</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D19" s="1"/>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2689,11 +2762,11 @@
         <v>5020</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D20" s="1"/>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2701,10 +2774,10 @@
         <v>5030</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:6">
@@ -2712,10 +2785,10 @@
         <v>5040</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:6">
@@ -2723,10 +2796,10 @@
         <v>6010</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2734,10 +2807,10 @@
         <v>7010</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F24" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2745,10 +2818,10 @@
         <v>7020</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Equipments" sheetId="1" r:id="rId1"/>
@@ -225,22 +225,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,13 +246,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -269,9 +254,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,14 +271,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -308,17 +284,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,28 +315,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -367,6 +360,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -377,31 +377,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,7 +503,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,133 +545,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,16 +590,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,6 +606,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,30 +660,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -676,7 +676,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -685,136 +685,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1744,7 +1744,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1774,7 +1774,7 @@
         <v>11010</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>501010</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1799,10 +1799,10 @@
         <v>1020</v>
       </c>
       <c r="B4">
-        <v>11110</v>
+        <v>11020</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>501020</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1827,10 +1827,10 @@
         <v>1030</v>
       </c>
       <c r="B6">
-        <v>11080</v>
+        <v>11030</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>501030</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1855,13 +1855,13 @@
         <v>1040</v>
       </c>
       <c r="B8">
-        <v>501040</v>
+        <v>11040</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1869,13 +1869,13 @@
         <v>1040</v>
       </c>
       <c r="B9">
-        <v>501041</v>
+        <v>501040</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1883,10 +1883,10 @@
         <v>2010</v>
       </c>
       <c r="B10">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>502010</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1911,10 +1911,10 @@
         <v>2020</v>
       </c>
       <c r="B12">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>502020</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         <v>2030</v>
       </c>
       <c r="B14">
-        <v>12050</v>
+        <v>12030</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1956,7 +1956,7 @@
         <v>502030</v>
       </c>
       <c r="C15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1967,13 +1967,13 @@
         <v>2040</v>
       </c>
       <c r="B16">
-        <v>502040</v>
+        <v>12040</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1981,13 +1981,13 @@
         <v>2040</v>
       </c>
       <c r="B17">
-        <v>502041</v>
+        <v>502040</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>13010</v>
       </c>
       <c r="C18">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>503010</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>3020</v>
       </c>
       <c r="B20">
-        <v>13120</v>
+        <v>13020</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>503020</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2051,10 +2051,10 @@
         <v>3030</v>
       </c>
       <c r="B22">
-        <v>13130</v>
+        <v>13030</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>503030</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2079,13 +2079,13 @@
         <v>3040</v>
       </c>
       <c r="B24">
-        <v>503040</v>
+        <v>13040</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2093,13 +2093,13 @@
         <v>3040</v>
       </c>
       <c r="B25">
-        <v>503041</v>
+        <v>503040</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2107,10 +2107,10 @@
         <v>4010</v>
       </c>
       <c r="B26">
-        <v>14050</v>
+        <v>14010</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>504010</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>4020</v>
       </c>
       <c r="B28">
-        <v>14120</v>
+        <v>14020</v>
       </c>
       <c r="C28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>504020</v>
       </c>
       <c r="C29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2166,7 +2166,7 @@
         <v>14030</v>
       </c>
       <c r="C30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>504030</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2191,24 +2191,24 @@
         <v>4040</v>
       </c>
       <c r="B32">
-        <v>504040</v>
+        <v>14040</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>5010</v>
+        <v>4040</v>
       </c>
       <c r="B33">
-        <v>15120</v>
+        <v>504040</v>
       </c>
       <c r="C33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>5010</v>
       </c>
       <c r="B34">
-        <v>505010</v>
+        <v>15010</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2230,13 +2230,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B35">
-        <v>15010</v>
+        <v>505010</v>
       </c>
       <c r="C35">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2247,10 +2247,10 @@
         <v>5020</v>
       </c>
       <c r="B36">
-        <v>505020</v>
+        <v>15020</v>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2258,13 +2258,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B37">
-        <v>15130</v>
+        <v>505020</v>
       </c>
       <c r="C37">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2275,10 +2275,10 @@
         <v>5030</v>
       </c>
       <c r="B38">
-        <v>505030</v>
+        <v>15030</v>
       </c>
       <c r="C38">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2286,13 +2286,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B39">
-        <v>505040</v>
+        <v>505030</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2300,30 +2300,30 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>6010</v>
+        <v>5040</v>
       </c>
       <c r="B40">
-        <v>506010</v>
+        <v>15040</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>6010</v>
+        <v>5040</v>
       </c>
       <c r="B41">
-        <v>506011</v>
+        <v>505040</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2331,7 +2331,7 @@
         <v>6010</v>
       </c>
       <c r="B42">
-        <v>506012</v>
+        <v>506010</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>6010</v>
       </c>
       <c r="B43">
-        <v>506013</v>
+        <v>506011</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>7010</v>
+        <v>6010</v>
       </c>
       <c r="B44">
-        <v>507010</v>
+        <v>506012</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2370,32 +2370,54 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
+        <v>6010</v>
+      </c>
+      <c r="B45">
+        <v>506013</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>7010</v>
+      </c>
+      <c r="B46">
+        <v>507010</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
         <v>7020</v>
       </c>
-      <c r="B45">
+      <c r="B47">
         <v>507020</v>
       </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46"/>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="3"/>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="2:2">
-      <c r="B48" s="3"/>
+      <c r="B48"/>
     </row>
     <row r="49" spans="2:2">
-      <c r="B49"/>
+      <c r="B49" s="3"/>
     </row>
     <row r="50" spans="2:2">
-      <c r="B50"/>
+      <c r="B50" s="3"/>
     </row>
     <row r="51" spans="2:2">
       <c r="B51"/>
@@ -2482,16 +2504,16 @@
       <c r="B78"/>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79" s="3"/>
+      <c r="B79"/>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80" s="3"/>
+      <c r="B80"/>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81"/>
+      <c r="B81" s="3"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82"/>
+      <c r="B82" s="3"/>
     </row>
     <row r="83" spans="2:2">
       <c r="B83"/>
@@ -2501,6 +2523,12 @@
     </row>
     <row r="85" spans="2:2">
       <c r="B85"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>Id</t>
   </si>
@@ -184,6 +184,36 @@
   </si>
   <si>
     <t>New Recruit Bangle</t>
+  </si>
+  <si>
+    <t>炎のタリスマン</t>
+  </si>
+  <si>
+    <t>Talisman of Fire</t>
+  </si>
+  <si>
+    <t>雷のタリスマン</t>
+  </si>
+  <si>
+    <t>Talisman of Thunder</t>
+  </si>
+  <si>
+    <t>氷のタリスマン</t>
+  </si>
+  <si>
+    <t>Talisman of Ice</t>
+  </si>
+  <si>
+    <t>光のタリスマン</t>
+  </si>
+  <si>
+    <t>Talisman of Shine</t>
+  </si>
+  <si>
+    <t>闇のタリスマン</t>
+  </si>
+  <si>
+    <t>Talisman of Dark</t>
   </si>
   <si>
     <t>ルーンのエングレ</t>
@@ -224,15 +254,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,6 +275,21 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -261,44 +308,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -306,39 +315,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -353,16 +352,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -377,19 +407,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +419,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,91 +449,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,7 +473,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,31 +539,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,6 +598,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -582,15 +636,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,17 +655,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,15 +669,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -676,7 +706,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -685,16 +715,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -703,118 +733,118 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1182,7 +1212,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1692,45 +1722,150 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="B24">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>ルーンのエングレ</v>
+        <v>炎のタリスマン</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" customFormat="1" spans="1:6">
       <c r="A25">
-        <v>7020</v>
+        <v>6030</v>
       </c>
       <c r="B25">
-        <v>7020</v>
+        <v>6030</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>ドヴェルグの指輪</v>
+        <v>雷のタリスマン</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:6">
+      <c r="A26">
+        <v>6040</v>
+      </c>
+      <c r="B26">
+        <v>6040</v>
+      </c>
+      <c r="C26" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
+        <v>氷のタリスマン</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:6">
+      <c r="A27">
+        <v>6050</v>
+      </c>
+      <c r="B27">
+        <v>6050</v>
+      </c>
+      <c r="C27" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
+        <v>光のタリスマン</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
+      <c r="A28">
+        <v>6060</v>
+      </c>
+      <c r="B28">
+        <v>6060</v>
+      </c>
+      <c r="C28" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
+        <v>闇のタリスマン</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>7010</v>
+      </c>
+      <c r="B29">
+        <v>7010</v>
+      </c>
+      <c r="C29" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
+        <v>ルーンのエングレ</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
         <v>11</v>
       </c>
-      <c r="F25">
+      <c r="F29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>7020</v>
+      </c>
+      <c r="B30">
+        <v>7020</v>
+      </c>
+      <c r="C30" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
+        <v>ドヴェルグの指輪</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>11</v>
+      </c>
+      <c r="F30">
         <v>6</v>
       </c>
     </row>
@@ -1744,7 +1879,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2384,85 +2519,250 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="B46">
-        <v>507010</v>
+        <v>1010</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
+        <v>6020</v>
+      </c>
+      <c r="B47">
+        <v>506020</v>
+      </c>
+      <c r="C47">
+        <v>10</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>6020</v>
+      </c>
+      <c r="B48">
+        <v>11050</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>6030</v>
+      </c>
+      <c r="B49">
+        <v>2010</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>6030</v>
+      </c>
+      <c r="B50">
+        <v>506030</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>6030</v>
+      </c>
+      <c r="B51">
+        <v>12050</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>6040</v>
+      </c>
+      <c r="B52">
+        <v>3010</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>6040</v>
+      </c>
+      <c r="B53">
+        <v>506040</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>6040</v>
+      </c>
+      <c r="B54">
+        <v>13050</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>6050</v>
+      </c>
+      <c r="B55">
+        <v>4010</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>6050</v>
+      </c>
+      <c r="B56">
+        <v>506050</v>
+      </c>
+      <c r="C56">
+        <v>10</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>6050</v>
+      </c>
+      <c r="B57">
+        <v>14050</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>6060</v>
+      </c>
+      <c r="B58">
+        <v>5010</v>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>6060</v>
+      </c>
+      <c r="B59">
+        <v>506060</v>
+      </c>
+      <c r="C59">
+        <v>10</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>6060</v>
+      </c>
+      <c r="B60">
+        <v>15050</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>7010</v>
+      </c>
+      <c r="B61">
+        <v>507010</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62">
         <v>7020</v>
       </c>
-      <c r="B47">
+      <c r="B62">
         <v>507020</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48"/>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="3"/>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="3"/>
-    </row>
-    <row r="51" spans="2:2">
-      <c r="B51"/>
-    </row>
-    <row r="52" spans="2:2">
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55"/>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56"/>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57"/>
-    </row>
-    <row r="58" spans="2:2">
-      <c r="B58"/>
-    </row>
-    <row r="59" spans="2:2">
-      <c r="B59"/>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60"/>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61"/>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62"/>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63"/>
     </row>
     <row r="64" spans="2:2">
-      <c r="B64"/>
+      <c r="B64" s="3"/>
     </row>
     <row r="65" spans="2:2">
-      <c r="B65"/>
+      <c r="B65" s="3"/>
     </row>
     <row r="66" spans="2:2">
       <c r="B66"/>
@@ -2510,10 +2810,10 @@
       <c r="B80"/>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="3"/>
+      <c r="B81"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="3"/>
+      <c r="B82"/>
     </row>
     <row r="83" spans="2:2">
       <c r="B83"/>
@@ -2529,6 +2829,51 @@
     </row>
     <row r="87" spans="2:2">
       <c r="B87"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2539,7 +2884,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
@@ -2830,9 +3175,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24">
-        <v>7010</v>
+        <v>6020</v>
       </c>
       <c r="B24" t="s">
         <v>56</v>
@@ -2841,15 +3186,70 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" customFormat="1" spans="1:6">
       <c r="A25">
-        <v>7020</v>
+        <v>6030</v>
       </c>
       <c r="B25" t="s">
         <v>58</v>
       </c>
       <c r="F25" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:6">
+      <c r="A26">
+        <v>6040</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:6">
+      <c r="A27">
+        <v>6050</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
+      <c r="A28">
+        <v>6060</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>7010</v>
+      </c>
+      <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>7020</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Equipments.xlsx
+++ b/Assets/Data/Equipments.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -84,6 +84,12 @@
     <t>Avatar of Flame Belt</t>
   </si>
   <si>
+    <t>ボルグの熱石</t>
+  </si>
+  <si>
+    <t>シンモラのピアス</t>
+  </si>
+  <si>
     <t>雷の結晶</t>
   </si>
   <si>
@@ -108,6 +114,12 @@
     <t>Lightning Talisman</t>
   </si>
   <si>
+    <t>トールズリング</t>
+  </si>
+  <si>
+    <t>放電の耳飾り</t>
+  </si>
+  <si>
     <t>ブリザードアンク</t>
   </si>
   <si>
@@ -132,6 +144,9 @@
     <t>Giant's Collar</t>
   </si>
   <si>
+    <t>氷河の涙石</t>
+  </si>
+  <si>
     <t>アルフの光羽</t>
   </si>
   <si>
@@ -156,6 +171,12 @@
     <t>Earth Brooch</t>
   </si>
   <si>
+    <t>妖精の羽飾り</t>
+  </si>
+  <si>
+    <t>ダグの光冠</t>
+  </si>
+  <si>
     <t>邪神のリング</t>
   </si>
   <si>
@@ -178,6 +199,12 @@
   </si>
   <si>
     <t>Uot's Illusion Mirror</t>
+  </si>
+  <si>
+    <t>影の腕輪</t>
+  </si>
+  <si>
+    <t>フェンリルの牙</t>
   </si>
   <si>
     <t>新兵のバングル</t>
@@ -234,9 +261,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -254,6 +281,82 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -262,9 +365,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,83 +403,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -382,17 +418,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -407,7 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,7 +464,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,37 +572,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,37 +584,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,43 +602,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,25 +614,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,25 +628,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -636,6 +654,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,8 +687,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -667,34 +696,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -706,145 +733,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1212,7 +1239,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="14.6272727272727" customWidth="1"/>
@@ -1365,58 +1392,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" customFormat="1" spans="1:6">
       <c r="A7">
-        <v>2010</v>
+        <v>1110</v>
       </c>
       <c r="B7">
-        <v>2010</v>
+        <v>1110</v>
       </c>
       <c r="C7" t="str">
         <f>INDEX(TextData!B:B,MATCH(B7,TextData!A:A))</f>
-        <v>雷の結晶</v>
+        <v>ボルグの熱石</v>
       </c>
       <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
       <c r="F7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
       <c r="A8">
-        <v>2020</v>
+        <v>1120</v>
       </c>
       <c r="B8">
-        <v>2020</v>
+        <v>1120</v>
       </c>
       <c r="C8" t="str">
         <f>INDEX(TextData!B:B,MATCH(B8,TextData!A:A))</f>
-        <v>トルドの雷針</v>
+        <v>シンモラのピアス</v>
       </c>
       <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>2</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="B9">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="C9" t="str">
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
-        <v>雷神の指輪</v>
+        <v>雷の結晶</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1428,16 +1455,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10">
-        <v>2040</v>
+        <v>2020</v>
       </c>
       <c r="B10">
-        <v>2040</v>
+        <v>2020</v>
       </c>
       <c r="C10" t="str">
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
-        <v>電撃のタリスマン</v>
+        <v>トルドの雷針</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1451,421 +1478,631 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B11">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="C11" t="str">
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
-        <v>ブリザードアンク</v>
+        <v>雷神の指輪</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
       <c r="A12">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="B12">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="C12" t="str">
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
-        <v>氷風の耳飾り</v>
+        <v>電撃のタリスマン</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
       <c r="A13">
-        <v>3030</v>
+        <v>2110</v>
       </c>
       <c r="B13">
-        <v>3030</v>
+        <v>2110</v>
       </c>
       <c r="C13" t="str">
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
-        <v>スヴェルの結界</v>
+        <v>トールズリング</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:6">
       <c r="A14">
-        <v>3040</v>
+        <v>2120</v>
       </c>
       <c r="B14">
-        <v>3040</v>
+        <v>2120</v>
       </c>
       <c r="C14" t="str">
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
-        <v>巨人の首輪</v>
+        <v>放電の耳飾り</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>4010</v>
+        <v>3010</v>
       </c>
       <c r="B15">
-        <v>4010</v>
+        <v>3010</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>アルフの光羽</v>
+        <v>ブリザードアンク</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>4020</v>
+        <v>3020</v>
       </c>
       <c r="B16">
-        <v>4020</v>
+        <v>3020</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>聖光のリボン</v>
+        <v>氷風の耳飾り</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>4030</v>
+        <v>3030</v>
       </c>
       <c r="B17">
-        <v>4030</v>
+        <v>3030</v>
       </c>
       <c r="C17" t="str">
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
-        <v>グリンの金剛毛</v>
+        <v>スヴェルの結界</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:6">
       <c r="A18">
-        <v>4040</v>
+        <v>3040</v>
       </c>
       <c r="B18">
-        <v>4040</v>
+        <v>3040</v>
       </c>
       <c r="C18" t="str">
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
-        <v>アースブローチ</v>
+        <v>巨人の首輪</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:6">
       <c r="A19">
-        <v>5010</v>
+        <v>3110</v>
       </c>
       <c r="B19">
-        <v>5010</v>
+        <v>3110</v>
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
-        <v>邪神のリング</v>
+        <v>スヴェルの結界</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:6">
       <c r="A20">
-        <v>5020</v>
+        <v>3120</v>
       </c>
       <c r="B20">
-        <v>5020</v>
+        <v>3120</v>
       </c>
       <c r="C20" t="str">
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
-        <v>ヨルムの魔鱗</v>
+        <v>氷河の涙石</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>5030</v>
+        <v>4010</v>
       </c>
       <c r="B21">
-        <v>5030</v>
+        <v>4010</v>
       </c>
       <c r="C21" t="str">
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
-        <v>ナグルファル片</v>
+        <v>アルフの光羽</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
-        <v>5040</v>
+        <v>4020</v>
       </c>
       <c r="B22">
-        <v>5040</v>
+        <v>4020</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>ウートの幻影鏡</v>
+        <v>聖光のリボン</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
-        <v>6010</v>
+        <v>4030</v>
       </c>
       <c r="B23">
-        <v>6010</v>
+        <v>4030</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>新兵のバングル</v>
+        <v>グリンの金剛毛</v>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
-        <v>6020</v>
+        <v>4040</v>
       </c>
       <c r="B24">
-        <v>6020</v>
+        <v>4040</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>炎のタリスマン</v>
+        <v>アースブローチ</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:6">
       <c r="A25">
-        <v>6030</v>
+        <v>4110</v>
       </c>
       <c r="B25">
-        <v>6030</v>
+        <v>4110</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>雷のタリスマン</v>
+        <v>妖精の羽飾り</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:6">
       <c r="A26">
-        <v>6040</v>
+        <v>4120</v>
       </c>
       <c r="B26">
-        <v>6040</v>
+        <v>4120</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
-        <v>氷のタリスマン</v>
+        <v>ダグの光冠</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
-        <v>6050</v>
+        <v>5010</v>
       </c>
       <c r="B27">
-        <v>6050</v>
+        <v>5010</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
-        <v>光のタリスマン</v>
+        <v>邪神のリング</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
-        <v>6060</v>
+        <v>5020</v>
       </c>
       <c r="B28">
-        <v>6060</v>
+        <v>5020</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>闇のタリスマン</v>
+        <v>ヨルムの魔鱗</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>7010</v>
+        <v>5030</v>
       </c>
       <c r="B29">
-        <v>7010</v>
+        <v>5030</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>ルーンのエングレ</v>
+        <v>ナグルファル片</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
       <c r="A30">
-        <v>7020</v>
+        <v>5040</v>
       </c>
       <c r="B30">
-        <v>7020</v>
+        <v>5040</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
+        <v>ウートの幻影鏡</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
+      <c r="A31">
+        <v>5110</v>
+      </c>
+      <c r="B31">
+        <v>5110</v>
+      </c>
+      <c r="C31" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
+        <v>影の腕輪</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
+      <c r="A32">
+        <v>5120</v>
+      </c>
+      <c r="B32">
+        <v>5120</v>
+      </c>
+      <c r="C32" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
+        <v>フェンリルの牙</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
+      <c r="A33">
+        <v>6010</v>
+      </c>
+      <c r="B33">
+        <v>6010</v>
+      </c>
+      <c r="C33" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
+        <v>新兵のバングル</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
+      <c r="A34">
+        <v>6020</v>
+      </c>
+      <c r="B34">
+        <v>6020</v>
+      </c>
+      <c r="C34" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
+        <v>炎のタリスマン</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
+      <c r="A35">
+        <v>6030</v>
+      </c>
+      <c r="B35">
+        <v>6030</v>
+      </c>
+      <c r="C35" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
+        <v>雷のタリスマン</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
+      <c r="A36">
+        <v>6040</v>
+      </c>
+      <c r="B36">
+        <v>6040</v>
+      </c>
+      <c r="C36" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
+        <v>氷のタリスマン</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:6">
+      <c r="A37">
+        <v>6050</v>
+      </c>
+      <c r="B37">
+        <v>6050</v>
+      </c>
+      <c r="C37" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
+        <v>光のタリスマン</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:6">
+      <c r="A38">
+        <v>6060</v>
+      </c>
+      <c r="B38">
+        <v>6060</v>
+      </c>
+      <c r="C38" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
+        <v>闇のタリスマン</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>7010</v>
+      </c>
+      <c r="B39">
+        <v>7010</v>
+      </c>
+      <c r="C39" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
+        <v>ルーンのエングレ</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>11</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>7020</v>
+      </c>
+      <c r="B40">
+        <v>7020</v>
+      </c>
+      <c r="C40" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
         <v>ドヴェルグの指輪</v>
       </c>
-      <c r="D30">
+      <c r="D40">
         <v>6</v>
       </c>
-      <c r="E30">
+      <c r="E40">
         <v>11</v>
       </c>
-      <c r="F30">
+      <c r="F40">
         <v>6</v>
       </c>
     </row>
@@ -1879,7 +2116,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2015,27 +2252,27 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>2010</v>
+        <v>1110</v>
       </c>
       <c r="B10">
-        <v>12010</v>
+        <v>1020</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:4">
+    <row r="11" spans="1:4">
       <c r="A11">
-        <v>2010</v>
+        <v>1120</v>
       </c>
       <c r="B11">
-        <v>502010</v>
+        <v>1030</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2043,10 +2280,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B12">
-        <v>12020</v>
+        <v>12010</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -2055,12 +2292,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" customFormat="1" spans="1:4">
       <c r="A13">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B13">
-        <v>502020</v>
+        <v>502010</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -2071,10 +2308,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B14">
-        <v>12030</v>
+        <v>12020</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -2085,10 +2322,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B15">
-        <v>502030</v>
+        <v>502020</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -2099,10 +2336,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B16">
-        <v>12040</v>
+        <v>12030</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -2113,10 +2350,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B17">
-        <v>502040</v>
+        <v>502030</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -2127,10 +2364,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B18">
-        <v>13010</v>
+        <v>12040</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -2141,10 +2378,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B19">
-        <v>503010</v>
+        <v>502040</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -2155,13 +2392,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>3020</v>
+        <v>2110</v>
       </c>
       <c r="B20">
-        <v>13020</v>
+        <v>2020</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2169,13 +2406,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>3020</v>
+        <v>2120</v>
       </c>
       <c r="B21">
-        <v>503020</v>
+        <v>2030</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2183,10 +2420,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B22">
-        <v>13030</v>
+        <v>13010</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -2197,10 +2434,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B23">
-        <v>503030</v>
+        <v>503010</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -2211,10 +2448,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>3040</v>
+        <v>3020</v>
       </c>
       <c r="B24">
-        <v>13040</v>
+        <v>13020</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2225,10 +2462,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>3040</v>
+        <v>3020</v>
       </c>
       <c r="B25">
-        <v>503040</v>
+        <v>503020</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -2239,10 +2476,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B26">
-        <v>14010</v>
+        <v>13030</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -2253,10 +2490,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B27">
-        <v>504010</v>
+        <v>503030</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2267,10 +2504,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>4020</v>
+        <v>3040</v>
       </c>
       <c r="B28">
-        <v>14020</v>
+        <v>13040</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -2281,10 +2518,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>4020</v>
+        <v>3040</v>
       </c>
       <c r="B29">
-        <v>504020</v>
+        <v>503040</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -2295,13 +2532,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>4030</v>
+        <v>3110</v>
       </c>
       <c r="B30">
-        <v>14030</v>
+        <v>3020</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2309,13 +2546,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>4030</v>
+        <v>3120</v>
       </c>
       <c r="B31">
-        <v>504030</v>
+        <v>3030</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2323,10 +2560,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="B32">
-        <v>14040</v>
+        <v>14010</v>
       </c>
       <c r="C32">
         <v>10</v>
@@ -2337,10 +2574,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="B33">
-        <v>504040</v>
+        <v>504010</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -2351,10 +2588,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="B34">
-        <v>15010</v>
+        <v>14020</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -2365,10 +2602,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="B35">
-        <v>505010</v>
+        <v>504020</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -2379,10 +2616,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>5020</v>
+        <v>4030</v>
       </c>
       <c r="B36">
-        <v>15020</v>
+        <v>14030</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -2393,10 +2630,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>5020</v>
+        <v>4030</v>
       </c>
       <c r="B37">
-        <v>505020</v>
+        <v>504030</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -2407,10 +2644,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>5030</v>
+        <v>4040</v>
       </c>
       <c r="B38">
-        <v>15030</v>
+        <v>14040</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -2421,10 +2658,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>5030</v>
+        <v>4040</v>
       </c>
       <c r="B39">
-        <v>505030</v>
+        <v>504040</v>
       </c>
       <c r="C39">
         <v>10</v>
@@ -2435,13 +2672,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>5040</v>
+        <v>4110</v>
       </c>
       <c r="B40">
-        <v>15040</v>
+        <v>4020</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2449,13 +2686,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>5040</v>
+        <v>4120</v>
       </c>
       <c r="B41">
-        <v>505040</v>
+        <v>4030</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2463,66 +2700,66 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B42">
-        <v>506010</v>
+        <v>15010</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B43">
-        <v>506011</v>
+        <v>505010</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>6010</v>
+        <v>5020</v>
       </c>
       <c r="B44">
-        <v>506012</v>
+        <v>15020</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>6010</v>
+        <v>5020</v>
       </c>
       <c r="B45">
-        <v>506013</v>
+        <v>505020</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>6020</v>
+        <v>5030</v>
       </c>
       <c r="B46">
-        <v>1010</v>
+        <v>15030</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -2533,10 +2770,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>6020</v>
+        <v>5030</v>
       </c>
       <c r="B47">
-        <v>506020</v>
+        <v>505030</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2547,24 +2784,24 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>6020</v>
+        <v>5040</v>
       </c>
       <c r="B48">
-        <v>11050</v>
+        <v>15040</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>6030</v>
+        <v>5040</v>
       </c>
       <c r="B49">
-        <v>2010</v>
+        <v>505040</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -2575,13 +2812,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>6030</v>
+        <v>5110</v>
       </c>
       <c r="B50">
-        <v>506030</v>
+        <v>5020</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2589,52 +2826,52 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>6030</v>
+        <v>5120</v>
       </c>
       <c r="B51">
-        <v>12050</v>
+        <v>5030</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>6040</v>
+        <v>6010</v>
       </c>
       <c r="B52">
-        <v>3010</v>
+        <v>506010</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>6040</v>
+        <v>6010</v>
       </c>
       <c r="B53">
-        <v>506040</v>
+        <v>506011</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>6040</v>
+        <v>6010</v>
       </c>
       <c r="B54">
-        <v>13050</v>
+        <v>506012</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2645,27 +2882,27 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>6050</v>
+        <v>6010</v>
       </c>
       <c r="B55">
-        <v>4010</v>
+        <v>506013</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>6050</v>
+        <v>6020</v>
       </c>
       <c r="B56">
-        <v>506050</v>
+        <v>1010</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2673,41 +2910,41 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>6050</v>
+        <v>6020</v>
       </c>
       <c r="B57">
-        <v>14050</v>
+        <v>506020</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>6060</v>
+        <v>6020</v>
       </c>
       <c r="B58">
-        <v>5010</v>
+        <v>11050</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>6060</v>
+        <v>6030</v>
       </c>
       <c r="B59">
-        <v>506060</v>
+        <v>2010</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2715,24 +2952,24 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>6060</v>
+        <v>6030</v>
       </c>
       <c r="B60">
-        <v>15050</v>
+        <v>506030</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>7010</v>
+        <v>6030</v>
       </c>
       <c r="B61">
-        <v>507010</v>
+        <v>12050</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2743,56 +2980,166 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
+        <v>6040</v>
+      </c>
+      <c r="B62">
+        <v>3010</v>
+      </c>
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63">
+        <v>6040</v>
+      </c>
+      <c r="B63">
+        <v>506040</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64">
+        <v>6040</v>
+      </c>
+      <c r="B64">
+        <v>13050</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65">
+        <v>6050</v>
+      </c>
+      <c r="B65">
+        <v>4010</v>
+      </c>
+      <c r="C65">
+        <v>8</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66">
+        <v>6050</v>
+      </c>
+      <c r="B66">
+        <v>506050</v>
+      </c>
+      <c r="C66">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67">
+        <v>6050</v>
+      </c>
+      <c r="B67">
+        <v>14050</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68">
+        <v>6060</v>
+      </c>
+      <c r="B68">
+        <v>5010</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69">
+        <v>6060</v>
+      </c>
+      <c r="B69">
+        <v>506060</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70">
+        <v>6060</v>
+      </c>
+      <c r="B70">
+        <v>15050</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71">
+        <v>7010</v>
+      </c>
+      <c r="B71">
+        <v>507010</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72">
         <v>7020</v>
       </c>
-      <c r="B62">
+      <c r="B72">
         <v>507020</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="3"/>
-    </row>
-    <row r="65" spans="2:2">
-      <c r="B65" s="3"/>
-    </row>
-    <row r="66" spans="2:2">
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="2:2">
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="2:2">
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72"/>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73"/>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74"/>
+      <c r="B74" s="3"/>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75"/>
+      <c r="B75" s="3"/>
     </row>
     <row r="76" spans="2:2">
       <c r="B76"/>
@@ -2855,10 +3202,10 @@
       <c r="B95"/>
     </row>
     <row r="96" spans="2:2">
-      <c r="B96" s="3"/>
+      <c r="B96"/>
     </row>
     <row r="97" spans="2:2">
-      <c r="B97" s="3"/>
+      <c r="B97"/>
     </row>
     <row r="98" spans="2:2">
       <c r="B98"/>
@@ -2874,6 +3221,36 @@
     </row>
     <row r="102" spans="2:2">
       <c r="B102"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108"/>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109"/>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2884,7 +3261,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="16.0363636363636" customWidth="1"/>
@@ -2970,286 +3347,412 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>2010</v>
+        <v>1110</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>2020</v>
+        <v>1120</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>2040</v>
+        <v>2020</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>3020</v>
+        <v>2040</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>3030</v>
+        <v>2110</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>3040</v>
+        <v>2120</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>4010</v>
+        <v>3010</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>4020</v>
+        <v>3020</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1"/>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>4030</v>
+        <v>3030</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>4040</v>
+        <v>3040</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>5010</v>
+        <v>3110</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>5020</v>
+        <v>3120</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D20" s="1"/>
+      <c r="E20"/>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>5030</v>
+        <v>4010</v>
       </c>
       <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>4020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>4030</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>4040</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="F24" t="s">
         <v>50</v>
       </c>
-      <c r="F21" t="s">
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>4110</v>
+      </c>
+      <c r="B25" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:6">
-      <c r="A22">
-        <v>5040</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="D25" s="1"/>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>4120</v>
+      </c>
+      <c r="B26" t="s">
         <v>52</v>
       </c>
-      <c r="F22" t="s">
+      <c r="D26" s="1"/>
+      <c r="F26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>5010</v>
+      </c>
+      <c r="B27" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:6">
-      <c r="A23">
-        <v>6010</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="D27" s="1"/>
+      <c r="F27" t="s">
         <v>54</v>
       </c>
-      <c r="F23" t="s">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>5020</v>
+      </c>
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:6">
-      <c r="A24">
-        <v>6020</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="D28" s="1"/>
+      <c r="F28" t="s">
         <v>56</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:6">
-      <c r="A25">
-        <v>6030</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:6">
-      <c r="A26">
-        <v>6040</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:6">
-      <c r="A27">
-        <v>6050</v>
-      </c>
-      <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:6">
-      <c r="A28">
-        <v>6060</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
+        <v>5030</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
+      <c r="A30">
+        <v>5040</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
+      <c r="A31">
+        <v>5110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
+      <c r="A32">
+        <v>5120</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="F32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
+      <c r="A33">
+        <v>6010</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
+      <c r="A34">
+        <v>6020</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
+      <c r="A35">
+        <v>6030</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
+      <c r="A36">
+        <v>6040</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:6">
+      <c r="A37">
+        <v>6050</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:6">
+      <c r="A38">
+        <v>6060</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
         <v>7010</v>
       </c>
-      <c r="B29" t="s">
-        <v>66</v>
-      </c>
-      <c r="F29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
         <v>7020</v>
       </c>
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="F30" t="s">
-        <v>69</v>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
